--- a/data/raw/mayor_bancos_202603.xlsx
+++ b/data/raw/mayor_bancos_202603.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="240">
   <si>
     <t>Fch Mov</t>
   </si>
@@ -436,6 +436,9 @@
     <t>Liquidación Getnet 18/03</t>
   </si>
   <si>
+    <t>Pago OP 0001-000362 Seguros Proteccion SA</t>
+  </si>
+  <si>
     <t>Cobro FC A 0001-00001202 Figueroa</t>
   </si>
   <si>
@@ -557,6 +560,9 @@
   </si>
   <si>
     <t>Liquidación Getnet 24/03</t>
+  </si>
+  <si>
+    <t>Anulación asiento duplicado Pago OP 0001-000362 Seguros Proteccion SA</t>
   </si>
   <si>
     <t>Cobro FC A 0001-00001203 Ledesma</t>
@@ -1063,7 +1069,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H227"/>
+  <dimension ref="A1:H230"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1112,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H2" s="1">
         <v>46085</v>
@@ -1138,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H3" s="1">
         <v>46085</v>
@@ -1164,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H4" s="1">
         <v>46083</v>
@@ -1190,7 +1196,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H5" s="1">
         <v>46085</v>
@@ -1216,7 +1222,7 @@
         <v>2941548.6</v>
       </c>
       <c r="G6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H6" s="1">
         <v>46083</v>
@@ -1242,7 +1248,7 @@
         <v>1622256.34</v>
       </c>
       <c r="G7" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H7" s="1">
         <v>46084</v>
@@ -1268,7 +1274,7 @@
         <v>2801429.73</v>
       </c>
       <c r="G8" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H8" s="1">
         <v>46084</v>
@@ -1294,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H9" s="1">
         <v>46085</v>
@@ -1320,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H10" s="1">
         <v>46084</v>
@@ -1346,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H11" s="1">
         <v>46085</v>
@@ -1372,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H12" s="1">
         <v>46085</v>
@@ -1398,7 +1404,7 @@
         <v>2991182.62</v>
       </c>
       <c r="G13" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H13" s="1">
         <v>46086</v>
@@ -1424,7 +1430,7 @@
         <v>1897356.02</v>
       </c>
       <c r="G14" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H14" s="1">
         <v>46084</v>
@@ -1450,7 +1456,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H15" s="1">
         <v>46086</v>
@@ -1476,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H16" s="1">
         <v>46086</v>
@@ -1502,7 +1508,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H17" s="1">
         <v>46086</v>
@@ -1528,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H18" s="1">
         <v>46087</v>
@@ -1554,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H19" s="1">
         <v>46087</v>
@@ -1580,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H20" s="1">
         <v>46085</v>
@@ -1606,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H21" s="1">
         <v>46087</v>
@@ -1632,7 +1638,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H22" s="1">
         <v>46087</v>
@@ -1658,7 +1664,7 @@
         <v>2715971.99</v>
       </c>
       <c r="G23" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H23" s="1">
         <v>46086</v>
@@ -1684,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H24" s="1">
         <v>46087</v>
@@ -1710,7 +1716,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H25" s="1">
         <v>46088</v>
@@ -1736,7 +1742,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H26" s="1">
         <v>46088</v>
@@ -1762,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H27" s="1">
         <v>46086</v>
@@ -1788,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H28" s="1">
         <v>46087</v>
@@ -1814,7 +1820,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H29" s="1">
         <v>46087</v>
@@ -1840,7 +1846,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H30" s="1">
         <v>46088</v>
@@ -1866,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H31" s="1">
         <v>46088</v>
@@ -1892,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H32" s="1">
         <v>46088</v>
@@ -1918,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H33" s="1">
         <v>46087</v>
@@ -1944,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H34" s="1">
         <v>46088</v>
@@ -1970,7 +1976,7 @@
         <v>3288803.47</v>
       </c>
       <c r="G35" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H35" s="1">
         <v>46088</v>
@@ -1996,7 +2002,7 @@
         <v>526534.78</v>
       </c>
       <c r="G36" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H36" s="1">
         <v>46088</v>
@@ -2022,7 +2028,7 @@
         <v>813812.11</v>
       </c>
       <c r="G37" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H37" s="1">
         <v>46086</v>
@@ -2048,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H38" s="1">
         <v>46087</v>
@@ -2074,7 +2080,7 @@
         <v>7038930.75</v>
       </c>
       <c r="G39" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H39" s="1">
         <v>46086</v>
@@ -2100,7 +2106,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H40" s="1">
         <v>46088</v>
@@ -2126,7 +2132,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H41" s="1">
         <v>46088</v>
@@ -2152,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H42" s="1">
         <v>46088</v>
@@ -2178,7 +2184,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H43" s="1">
         <v>46089</v>
@@ -2204,7 +2210,7 @@
         <v>2282836.34</v>
       </c>
       <c r="G44" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H44" s="1">
         <v>46089</v>
@@ -2230,7 +2236,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H45" s="1">
         <v>46089</v>
@@ -2256,7 +2262,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H46" s="1">
         <v>46088</v>
@@ -2282,7 +2288,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H47" s="1">
         <v>46088</v>
@@ -2308,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H48" s="1">
         <v>46090</v>
@@ -2334,7 +2340,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H49" s="1">
         <v>46089</v>
@@ -2360,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H50" s="1">
         <v>46091</v>
@@ -2386,7 +2392,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H51" s="1">
         <v>46090</v>
@@ -2412,7 +2418,7 @@
         <v>3087963.12</v>
       </c>
       <c r="G52" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H52" s="1">
         <v>46091</v>
@@ -2438,7 +2444,7 @@
         <v>2489860.81</v>
       </c>
       <c r="G53" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H53" s="1">
         <v>46092</v>
@@ -2464,7 +2470,7 @@
         <v>2766564.33</v>
       </c>
       <c r="G54" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H54" s="1">
         <v>46090</v>
@@ -2490,7 +2496,7 @@
         <v>1861476.04</v>
       </c>
       <c r="G55" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H55" s="1">
         <v>46091</v>
@@ -2516,7 +2522,7 @@
         <v>1939636.42</v>
       </c>
       <c r="G56" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H56" s="1">
         <v>46090</v>
@@ -2542,7 +2548,7 @@
         <v>409903.89</v>
       </c>
       <c r="G57" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H57" s="1">
         <v>46090</v>
@@ -2568,7 +2574,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H58" s="1">
         <v>46092</v>
@@ -2594,7 +2600,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H59" s="1">
         <v>46091</v>
@@ -2620,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H60" s="1">
         <v>46091</v>
@@ -2646,7 +2652,7 @@
         <v>3366926.87</v>
       </c>
       <c r="G61" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H61" s="1">
         <v>46093</v>
@@ -2672,7 +2678,7 @@
         <v>1277266.23</v>
       </c>
       <c r="G62" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H62" s="1">
         <v>46092</v>
@@ -2698,7 +2704,7 @@
         <v>1295231.8</v>
       </c>
       <c r="G63" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H63" s="1">
         <v>46092</v>
@@ -2724,7 +2730,7 @@
         <v>155101.19</v>
       </c>
       <c r="G64" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H64" s="1">
         <v>46092</v>
@@ -2750,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H65" s="1">
         <v>46091</v>
@@ -2776,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H66" s="1">
         <v>46092</v>
@@ -2802,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H67" s="1">
         <v>46094</v>
@@ -2828,7 +2834,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H68" s="1">
         <v>46093</v>
@@ -2854,7 +2860,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H69" s="1">
         <v>46093</v>
@@ -2880,7 +2886,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H70" s="1">
         <v>46092</v>
@@ -2906,7 +2912,7 @@
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H71" s="1">
         <v>46094</v>
@@ -2932,7 +2938,7 @@
         <v>2765061.06</v>
       </c>
       <c r="G72" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H72" s="1">
         <v>46094</v>
@@ -2958,7 +2964,7 @@
         <v>2071506.91</v>
       </c>
       <c r="G73" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H73" s="1">
         <v>46093</v>
@@ -2984,7 +2990,7 @@
         <v>1759196.67</v>
       </c>
       <c r="G74" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H74" s="1">
         <v>46093</v>
@@ -3010,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H75" s="1">
         <v>46094</v>
@@ -3036,7 +3042,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H76" s="1">
         <v>46092</v>
@@ -3062,7 +3068,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H77" s="1">
         <v>46095</v>
@@ -3088,7 +3094,7 @@
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H78" s="1">
         <v>46095</v>
@@ -3114,7 +3120,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H79" s="1">
         <v>46095</v>
@@ -3140,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H80" s="1">
         <v>46093</v>
@@ -3166,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H81" s="1">
         <v>46094</v>
@@ -3192,7 +3198,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H82" s="1">
         <v>46095</v>
@@ -3218,7 +3224,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H83" s="1">
         <v>46094</v>
@@ -3244,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H84" s="1">
         <v>46093</v>
@@ -3270,7 +3276,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H85" s="1">
         <v>46093</v>
@@ -3296,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H86" s="1">
         <v>46095</v>
@@ -3322,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H87" s="1">
         <v>46095</v>
@@ -3348,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H88" s="1">
         <v>46094</v>
@@ -3374,7 +3380,7 @@
         <v>2957715.53</v>
       </c>
       <c r="G89" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H89" s="1">
         <v>46094</v>
@@ -3400,7 +3406,7 @@
         <v>1154716.96</v>
       </c>
       <c r="G90" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H90" s="1">
         <v>46093</v>
@@ -3426,7 +3432,7 @@
         <v>2302870.84</v>
       </c>
       <c r="G91" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H91" s="1">
         <v>46094</v>
@@ -3452,7 +3458,7 @@
         <v>3085351.96</v>
       </c>
       <c r="G92" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H92" s="1">
         <v>46093</v>
@@ -3478,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H93" s="1">
         <v>46094</v>
@@ -3504,7 +3510,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H94" s="1">
         <v>46095</v>
@@ -3530,7 +3536,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H95" s="1">
         <v>46096</v>
@@ -3556,7 +3562,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H96" s="1">
         <v>46094</v>
@@ -3582,7 +3588,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H97" s="1">
         <v>46094</v>
@@ -3608,7 +3614,7 @@
         <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H98" s="1">
         <v>46096</v>
@@ -3634,7 +3640,7 @@
         <v>0</v>
       </c>
       <c r="G99" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H99" s="1">
         <v>46096</v>
@@ -3660,7 +3666,7 @@
         <v>1544344.99</v>
       </c>
       <c r="G100" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H100" s="1">
         <v>46094</v>
@@ -3686,7 +3692,7 @@
         <v>1905090.27</v>
       </c>
       <c r="G101" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H101" s="1">
         <v>46095</v>
@@ -3712,7 +3718,7 @@
         <v>0</v>
       </c>
       <c r="G102" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H102" s="1">
         <v>46096</v>
@@ -3738,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G103" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H103" s="1">
         <v>46096</v>
@@ -3764,7 +3770,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H104" s="1">
         <v>46096</v>
@@ -3790,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H105" s="1">
         <v>46096</v>
@@ -3816,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H106" s="1">
         <v>46097</v>
@@ -3842,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H107" s="1">
         <v>46096</v>
@@ -3868,7 +3874,7 @@
         <v>0</v>
       </c>
       <c r="G108" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H108" s="1">
         <v>46096</v>
@@ -3894,7 +3900,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H109" s="1">
         <v>46096</v>
@@ -3920,7 +3926,7 @@
         <v>3249151.76</v>
       </c>
       <c r="G110" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H110" s="1">
         <v>46096</v>
@@ -3946,7 +3952,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H111" s="1">
         <v>46097</v>
@@ -3972,7 +3978,7 @@
         <v>3097491.76</v>
       </c>
       <c r="G112" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H112" s="1">
         <v>46098</v>
@@ -3998,7 +4004,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H113" s="1">
         <v>46098</v>
@@ -4024,7 +4030,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H114" s="1">
         <v>46099</v>
@@ -4050,7 +4056,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H115" s="1">
         <v>46098</v>
@@ -4076,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H116" s="1">
         <v>46098</v>
@@ -4102,7 +4108,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H117" s="1">
         <v>46099</v>
@@ -4128,7 +4134,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H118" s="1">
         <v>46099</v>
@@ -4154,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="G119" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H119" s="1">
         <v>46100</v>
@@ -4180,7 +4186,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H120" s="1">
         <v>46098</v>
@@ -4206,7 +4212,7 @@
         <v>0</v>
       </c>
       <c r="G121" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H121" s="1">
         <v>46099</v>
@@ -4232,7 +4238,7 @@
         <v>0</v>
       </c>
       <c r="G122" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H122" s="1">
         <v>46100</v>
@@ -4258,7 +4264,7 @@
         <v>993185.92</v>
       </c>
       <c r="G123" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H123" s="1">
         <v>46100</v>
@@ -4284,7 +4290,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H124" s="1">
         <v>46099</v>
@@ -4310,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H125" s="1">
         <v>46100</v>
@@ -4336,7 +4342,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H126" s="1">
         <v>46100</v>
@@ -4362,7 +4368,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H127" s="1">
         <v>46101</v>
@@ -4388,7 +4394,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H128" s="1">
         <v>46101</v>
@@ -4414,7 +4420,7 @@
         <v>2893431.15</v>
       </c>
       <c r="G129" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H129" s="1">
         <v>46100</v>
@@ -4440,7 +4446,7 @@
         <v>207258.3</v>
       </c>
       <c r="G130" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H130" s="1">
         <v>46101</v>
@@ -4466,7 +4472,7 @@
         <v>1368468.64</v>
       </c>
       <c r="G131" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H131" s="1">
         <v>46099</v>
@@ -4492,7 +4498,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H132" s="1">
         <v>46100</v>
@@ -4500,10 +4506,10 @@
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="1">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="B133">
-        <v>4502</v>
+        <v>4727</v>
       </c>
       <c r="C133" t="s">
         <v>8</v>
@@ -4512,16 +4518,16 @@
         <v>140</v>
       </c>
       <c r="E133">
-        <v>2399190.17</v>
+        <v>0</v>
       </c>
       <c r="F133">
-        <v>0</v>
+        <v>287640</v>
       </c>
       <c r="G133" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H133" s="1">
-        <v>46102</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -4529,7 +4535,7 @@
         <v>46100</v>
       </c>
       <c r="B134">
-        <v>4507</v>
+        <v>4502</v>
       </c>
       <c r="C134" t="s">
         <v>8</v>
@@ -4538,13 +4544,13 @@
         <v>141</v>
       </c>
       <c r="E134">
-        <v>2135700.13</v>
+        <v>2399190.17</v>
       </c>
       <c r="F134">
         <v>0</v>
       </c>
       <c r="G134" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H134" s="1">
         <v>46102</v>
@@ -4555,7 +4561,7 @@
         <v>46100</v>
       </c>
       <c r="B135">
-        <v>4553</v>
+        <v>4507</v>
       </c>
       <c r="C135" t="s">
         <v>8</v>
@@ -4564,16 +4570,16 @@
         <v>142</v>
       </c>
       <c r="E135">
-        <v>2027817.97</v>
+        <v>2135700.13</v>
       </c>
       <c r="F135">
         <v>0</v>
       </c>
       <c r="G135" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H135" s="1">
-        <v>46101</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -4581,7 +4587,7 @@
         <v>46100</v>
       </c>
       <c r="B136">
-        <v>4563</v>
+        <v>4553</v>
       </c>
       <c r="C136" t="s">
         <v>8</v>
@@ -4590,7 +4596,7 @@
         <v>143</v>
       </c>
       <c r="E136">
-        <v>1947460.41</v>
+        <v>2027817.97</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -4599,7 +4605,7 @@
         <v>237</v>
       </c>
       <c r="H136" s="1">
-        <v>46100</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -4607,7 +4613,7 @@
         <v>46100</v>
       </c>
       <c r="B137">
-        <v>4572</v>
+        <v>4563</v>
       </c>
       <c r="C137" t="s">
         <v>8</v>
@@ -4616,16 +4622,16 @@
         <v>144</v>
       </c>
       <c r="E137">
-        <v>961060.38</v>
+        <v>1947460.41</v>
       </c>
       <c r="F137">
         <v>0</v>
       </c>
       <c r="G137" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H137" s="1">
-        <v>46102</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -4633,7 +4639,7 @@
         <v>46100</v>
       </c>
       <c r="B138">
-        <v>4586</v>
+        <v>4572</v>
       </c>
       <c r="C138" t="s">
         <v>8</v>
@@ -4642,13 +4648,13 @@
         <v>145</v>
       </c>
       <c r="E138">
-        <v>72041.25</v>
+        <v>961060.38</v>
       </c>
       <c r="F138">
         <v>0</v>
       </c>
       <c r="G138" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H138" s="1">
         <v>46102</v>
@@ -4659,7 +4665,7 @@
         <v>46100</v>
       </c>
       <c r="B139">
-        <v>4600</v>
+        <v>4586</v>
       </c>
       <c r="C139" t="s">
         <v>8</v>
@@ -4668,13 +4674,13 @@
         <v>146</v>
       </c>
       <c r="E139">
-        <v>1628710.57</v>
+        <v>72041.25</v>
       </c>
       <c r="F139">
         <v>0</v>
       </c>
       <c r="G139" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H139" s="1">
         <v>46102</v>
@@ -4685,7 +4691,7 @@
         <v>46100</v>
       </c>
       <c r="B140">
-        <v>4623</v>
+        <v>4600</v>
       </c>
       <c r="C140" t="s">
         <v>8</v>
@@ -4694,16 +4700,16 @@
         <v>147</v>
       </c>
       <c r="E140">
-        <v>315569.64</v>
+        <v>1628710.57</v>
       </c>
       <c r="F140">
         <v>0</v>
       </c>
       <c r="G140" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H140" s="1">
-        <v>46100</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -4711,7 +4717,7 @@
         <v>46100</v>
       </c>
       <c r="B141">
-        <v>4693</v>
+        <v>4623</v>
       </c>
       <c r="C141" t="s">
         <v>8</v>
@@ -4720,13 +4726,13 @@
         <v>148</v>
       </c>
       <c r="E141">
-        <v>610896.55</v>
+        <v>315569.64</v>
       </c>
       <c r="F141">
         <v>0</v>
       </c>
       <c r="G141" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H141" s="1">
         <v>46100</v>
@@ -4734,10 +4740,10 @@
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="1">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="B142">
-        <v>4509</v>
+        <v>4693</v>
       </c>
       <c r="C142" t="s">
         <v>8</v>
@@ -4746,42 +4752,42 @@
         <v>149</v>
       </c>
       <c r="E142">
-        <v>1216853.69</v>
+        <v>610896.55</v>
       </c>
       <c r="F142">
         <v>0</v>
       </c>
       <c r="G142" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="H142" s="1">
-        <v>46101</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="1">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="B143">
-        <v>4521</v>
+        <v>4728</v>
       </c>
       <c r="C143" t="s">
         <v>8</v>
       </c>
       <c r="D143" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E143">
-        <v>1751046.98</v>
+        <v>0</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>287640</v>
       </c>
       <c r="G143" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H143" s="1">
-        <v>46102</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -4789,25 +4795,25 @@
         <v>46101</v>
       </c>
       <c r="B144">
-        <v>4532</v>
+        <v>4509</v>
       </c>
       <c r="C144" t="s">
         <v>8</v>
       </c>
       <c r="D144" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E144">
-        <v>1892738.12</v>
+        <v>1216853.69</v>
       </c>
       <c r="F144">
         <v>0</v>
       </c>
       <c r="G144" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H144" s="1">
-        <v>46102</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -4815,22 +4821,22 @@
         <v>46101</v>
       </c>
       <c r="B145">
-        <v>4555</v>
+        <v>4521</v>
       </c>
       <c r="C145" t="s">
         <v>8</v>
       </c>
       <c r="D145" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E145">
-        <v>518190.43</v>
+        <v>1751046.98</v>
       </c>
       <c r="F145">
         <v>0</v>
       </c>
       <c r="G145" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H145" s="1">
         <v>46102</v>
@@ -4841,25 +4847,25 @@
         <v>46101</v>
       </c>
       <c r="B146">
-        <v>4595</v>
+        <v>4532</v>
       </c>
       <c r="C146" t="s">
         <v>8</v>
       </c>
       <c r="D146" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E146">
-        <v>902983.24</v>
+        <v>1892738.12</v>
       </c>
       <c r="F146">
         <v>0</v>
       </c>
       <c r="G146" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H146" s="1">
-        <v>46103</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -4867,25 +4873,25 @@
         <v>46101</v>
       </c>
       <c r="B147">
-        <v>4608</v>
+        <v>4555</v>
       </c>
       <c r="C147" t="s">
         <v>8</v>
       </c>
       <c r="D147" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E147">
-        <v>1257149.42</v>
+        <v>518190.43</v>
       </c>
       <c r="F147">
         <v>0</v>
       </c>
       <c r="G147" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H147" s="1">
-        <v>46103</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -4893,22 +4899,22 @@
         <v>46101</v>
       </c>
       <c r="B148">
-        <v>4619</v>
+        <v>4595</v>
       </c>
       <c r="C148" t="s">
         <v>8</v>
       </c>
       <c r="D148" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E148">
-        <v>542342.8199999999</v>
+        <v>902983.24</v>
       </c>
       <c r="F148">
         <v>0</v>
       </c>
       <c r="G148" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H148" s="1">
         <v>46103</v>
@@ -4919,25 +4925,25 @@
         <v>46101</v>
       </c>
       <c r="B149">
-        <v>4663</v>
+        <v>4608</v>
       </c>
       <c r="C149" t="s">
         <v>8</v>
       </c>
       <c r="D149" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>1257149.42</v>
       </c>
       <c r="F149">
-        <v>2108049.15</v>
+        <v>0</v>
       </c>
       <c r="G149" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H149" s="1">
-        <v>46102</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -4945,25 +4951,25 @@
         <v>46101</v>
       </c>
       <c r="B150">
-        <v>4694</v>
+        <v>4619</v>
       </c>
       <c r="C150" t="s">
         <v>8</v>
       </c>
       <c r="D150" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E150">
-        <v>336801.22</v>
+        <v>542342.8199999999</v>
       </c>
       <c r="F150">
         <v>0</v>
       </c>
       <c r="G150" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H150" s="1">
-        <v>46101</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -4971,22 +4977,22 @@
         <v>46101</v>
       </c>
       <c r="B151">
-        <v>4703</v>
+        <v>4663</v>
       </c>
       <c r="C151" t="s">
         <v>8</v>
       </c>
       <c r="D151" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E151">
         <v>0</v>
       </c>
       <c r="F151">
-        <v>6216685.89</v>
+        <v>2108049.15</v>
       </c>
       <c r="G151" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H151" s="1">
         <v>46102</v>
@@ -4994,51 +5000,51 @@
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="1">
-        <v>46102</v>
+        <v>46101</v>
       </c>
       <c r="B152">
-        <v>4535</v>
+        <v>4694</v>
       </c>
       <c r="C152" t="s">
         <v>8</v>
       </c>
       <c r="D152" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E152">
-        <v>1634314.82</v>
+        <v>336801.22</v>
       </c>
       <c r="F152">
         <v>0</v>
       </c>
       <c r="G152" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H152" s="1">
-        <v>46104</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="1">
-        <v>46102</v>
+        <v>46101</v>
       </c>
       <c r="B153">
-        <v>4573</v>
+        <v>4703</v>
       </c>
       <c r="C153" t="s">
         <v>8</v>
       </c>
       <c r="D153" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E153">
-        <v>1010127.77</v>
+        <v>0</v>
       </c>
       <c r="F153">
-        <v>0</v>
+        <v>6216685.89</v>
       </c>
       <c r="G153" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H153" s="1">
         <v>46102</v>
@@ -5049,22 +5055,22 @@
         <v>46102</v>
       </c>
       <c r="B154">
-        <v>4576</v>
+        <v>4535</v>
       </c>
       <c r="C154" t="s">
         <v>8</v>
       </c>
       <c r="D154" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E154">
-        <v>2012060.91</v>
+        <v>1634314.82</v>
       </c>
       <c r="F154">
         <v>0</v>
       </c>
       <c r="G154" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H154" s="1">
         <v>46104</v>
@@ -5075,65 +5081,65 @@
         <v>46102</v>
       </c>
       <c r="B155">
-        <v>4627</v>
+        <v>4573</v>
       </c>
       <c r="C155" t="s">
         <v>8</v>
       </c>
       <c r="D155" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E155">
-        <v>300000</v>
+        <v>1010127.77</v>
       </c>
       <c r="F155">
         <v>0</v>
       </c>
       <c r="G155" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H155" s="1">
-        <v>46103</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="1">
-        <v>46103</v>
+        <v>46102</v>
       </c>
       <c r="B156">
-        <v>4530</v>
+        <v>4576</v>
       </c>
       <c r="C156" t="s">
         <v>8</v>
       </c>
       <c r="D156" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E156">
-        <v>1374110.05</v>
+        <v>2012060.91</v>
       </c>
       <c r="F156">
         <v>0</v>
       </c>
       <c r="G156" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="H156" s="1">
-        <v>46103</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="1">
-        <v>46103</v>
+        <v>46102</v>
       </c>
       <c r="B157">
-        <v>4626</v>
+        <v>4627</v>
       </c>
       <c r="C157" t="s">
         <v>8</v>
       </c>
       <c r="D157" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E157">
         <v>300000</v>
@@ -5142,27 +5148,27 @@
         <v>0</v>
       </c>
       <c r="G157" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H157" s="1">
-        <v>46105</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="1">
-        <v>46104</v>
+        <v>46103</v>
       </c>
       <c r="B158">
-        <v>4577</v>
+        <v>4530</v>
       </c>
       <c r="C158" t="s">
         <v>8</v>
       </c>
       <c r="D158" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E158">
-        <v>274653.59</v>
+        <v>1374110.05</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -5171,33 +5177,33 @@
         <v>237</v>
       </c>
       <c r="H158" s="1">
-        <v>46105</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="1">
-        <v>46104</v>
+        <v>46103</v>
       </c>
       <c r="B159">
-        <v>4637</v>
+        <v>4626</v>
       </c>
       <c r="C159" t="s">
         <v>8</v>
       </c>
       <c r="D159" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E159">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="F159">
-        <v>3014086.36</v>
+        <v>0</v>
       </c>
       <c r="G159" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H159" s="1">
-        <v>46106</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -5205,25 +5211,25 @@
         <v>46104</v>
       </c>
       <c r="B160">
-        <v>4646</v>
+        <v>4577</v>
       </c>
       <c r="C160" t="s">
         <v>8</v>
       </c>
       <c r="D160" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E160">
-        <v>0</v>
+        <v>274653.59</v>
       </c>
       <c r="F160">
-        <v>2100649.72</v>
+        <v>0</v>
       </c>
       <c r="G160" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H160" s="1">
-        <v>46104</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -5231,25 +5237,25 @@
         <v>46104</v>
       </c>
       <c r="B161">
-        <v>4647</v>
+        <v>4637</v>
       </c>
       <c r="C161" t="s">
         <v>8</v>
       </c>
       <c r="D161" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E161">
         <v>0</v>
       </c>
       <c r="F161">
-        <v>1724587.69</v>
+        <v>3014086.36</v>
       </c>
       <c r="G161" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H161" s="1">
-        <v>46105</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -5257,22 +5263,22 @@
         <v>46104</v>
       </c>
       <c r="B162">
-        <v>4695</v>
+        <v>4646</v>
       </c>
       <c r="C162" t="s">
         <v>8</v>
       </c>
       <c r="D162" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E162">
-        <v>771525.6899999999</v>
+        <v>0</v>
       </c>
       <c r="F162">
-        <v>0</v>
+        <v>2100649.72</v>
       </c>
       <c r="G162" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H162" s="1">
         <v>46104</v>
@@ -5280,54 +5286,54 @@
     </row>
     <row r="163" spans="1:8">
       <c r="A163" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B163">
+        <v>4647</v>
+      </c>
+      <c r="C163" t="s">
+        <v>8</v>
+      </c>
+      <c r="D163" t="s">
+        <v>169</v>
+      </c>
+      <c r="E163">
+        <v>0</v>
+      </c>
+      <c r="F163">
+        <v>1724587.69</v>
+      </c>
+      <c r="G163" t="s">
+        <v>237</v>
+      </c>
+      <c r="H163" s="1">
         <v>46105</v>
-      </c>
-      <c r="B163">
-        <v>4504</v>
-      </c>
-      <c r="C163" t="s">
-        <v>8</v>
-      </c>
-      <c r="D163" t="s">
-        <v>170</v>
-      </c>
-      <c r="E163">
-        <v>1689551.98</v>
-      </c>
-      <c r="F163">
-        <v>0</v>
-      </c>
-      <c r="G163" t="s">
-        <v>236</v>
-      </c>
-      <c r="H163" s="1">
-        <v>46106</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" s="1">
-        <v>46105</v>
+        <v>46104</v>
       </c>
       <c r="B164">
-        <v>4505</v>
+        <v>4695</v>
       </c>
       <c r="C164" t="s">
         <v>8</v>
       </c>
       <c r="D164" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E164">
-        <v>654547.37</v>
+        <v>771525.6899999999</v>
       </c>
       <c r="F164">
         <v>0</v>
       </c>
       <c r="G164" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="H164" s="1">
-        <v>46107</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -5335,25 +5341,25 @@
         <v>46105</v>
       </c>
       <c r="B165">
-        <v>4525</v>
+        <v>4504</v>
       </c>
       <c r="C165" t="s">
         <v>8</v>
       </c>
       <c r="D165" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E165">
-        <v>2059665.24</v>
+        <v>1689551.98</v>
       </c>
       <c r="F165">
         <v>0</v>
       </c>
       <c r="G165" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H165" s="1">
-        <v>46105</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="166" spans="1:8">
@@ -5361,25 +5367,25 @@
         <v>46105</v>
       </c>
       <c r="B166">
-        <v>4549</v>
+        <v>4505</v>
       </c>
       <c r="C166" t="s">
         <v>8</v>
       </c>
       <c r="D166" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E166">
-        <v>1083769.09</v>
+        <v>654547.37</v>
       </c>
       <c r="F166">
         <v>0</v>
       </c>
       <c r="G166" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H166" s="1">
-        <v>46105</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -5387,22 +5393,22 @@
         <v>46105</v>
       </c>
       <c r="B167">
-        <v>4565</v>
+        <v>4525</v>
       </c>
       <c r="C167" t="s">
         <v>8</v>
       </c>
       <c r="D167" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E167">
-        <v>359474.62</v>
+        <v>2059665.24</v>
       </c>
       <c r="F167">
         <v>0</v>
       </c>
       <c r="G167" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H167" s="1">
         <v>46105</v>
@@ -5413,25 +5419,25 @@
         <v>46105</v>
       </c>
       <c r="B168">
-        <v>4569</v>
+        <v>4549</v>
       </c>
       <c r="C168" t="s">
         <v>8</v>
       </c>
       <c r="D168" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E168">
-        <v>1912728.46</v>
+        <v>1083769.09</v>
       </c>
       <c r="F168">
         <v>0</v>
       </c>
       <c r="G168" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H168" s="1">
-        <v>46107</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -5439,25 +5445,25 @@
         <v>46105</v>
       </c>
       <c r="B169">
-        <v>4598</v>
+        <v>4565</v>
       </c>
       <c r="C169" t="s">
         <v>8</v>
       </c>
       <c r="D169" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E169">
-        <v>2247327.38</v>
+        <v>359474.62</v>
       </c>
       <c r="F169">
         <v>0</v>
       </c>
       <c r="G169" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H169" s="1">
-        <v>46106</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -5465,16 +5471,16 @@
         <v>46105</v>
       </c>
       <c r="B170">
-        <v>4601</v>
+        <v>4569</v>
       </c>
       <c r="C170" t="s">
         <v>8</v>
       </c>
       <c r="D170" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E170">
-        <v>1973633.07</v>
+        <v>1912728.46</v>
       </c>
       <c r="F170">
         <v>0</v>
@@ -5491,25 +5497,25 @@
         <v>46105</v>
       </c>
       <c r="B171">
-        <v>4644</v>
+        <v>4598</v>
       </c>
       <c r="C171" t="s">
         <v>8</v>
       </c>
       <c r="D171" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E171">
-        <v>0</v>
+        <v>2247327.38</v>
       </c>
       <c r="F171">
-        <v>1645214.19</v>
+        <v>0</v>
       </c>
       <c r="G171" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H171" s="1">
-        <v>46107</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -5517,22 +5523,22 @@
         <v>46105</v>
       </c>
       <c r="B172">
-        <v>4660</v>
+        <v>4601</v>
       </c>
       <c r="C172" t="s">
         <v>8</v>
       </c>
       <c r="D172" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E172">
-        <v>0</v>
+        <v>1973633.07</v>
       </c>
       <c r="F172">
-        <v>1087665.02</v>
+        <v>0</v>
       </c>
       <c r="G172" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H172" s="1">
         <v>46107</v>
@@ -5543,100 +5549,100 @@
         <v>46105</v>
       </c>
       <c r="B173">
-        <v>4696</v>
+        <v>4644</v>
       </c>
       <c r="C173" t="s">
         <v>8</v>
       </c>
       <c r="D173" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E173">
-        <v>595329.5</v>
+        <v>0</v>
       </c>
       <c r="F173">
-        <v>0</v>
+        <v>1645214.19</v>
       </c>
       <c r="G173" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H173" s="1">
-        <v>46105</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" s="1">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="B174">
-        <v>4503</v>
+        <v>4660</v>
       </c>
       <c r="C174" t="s">
         <v>8</v>
       </c>
       <c r="D174" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E174">
-        <v>654105.28</v>
+        <v>0</v>
       </c>
       <c r="F174">
-        <v>0</v>
+        <v>1087665.02</v>
       </c>
       <c r="G174" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H174" s="1">
-        <v>46108</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" s="1">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="B175">
-        <v>4508</v>
+        <v>4696</v>
       </c>
       <c r="C175" t="s">
         <v>8</v>
       </c>
       <c r="D175" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E175">
-        <v>985014.9</v>
+        <v>595329.5</v>
       </c>
       <c r="F175">
         <v>0</v>
       </c>
       <c r="G175" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H175" s="1">
-        <v>46107</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" s="1">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="B176">
-        <v>4526</v>
+        <v>4729</v>
       </c>
       <c r="C176" t="s">
         <v>8</v>
       </c>
       <c r="D176" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E176">
-        <v>1676898.11</v>
+        <v>287640</v>
       </c>
       <c r="F176">
         <v>0</v>
       </c>
       <c r="G176" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H176" s="1">
         <v>46107</v>
@@ -5647,16 +5653,16 @@
         <v>46106</v>
       </c>
       <c r="B177">
-        <v>4562</v>
+        <v>4503</v>
       </c>
       <c r="C177" t="s">
         <v>8</v>
       </c>
       <c r="D177" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E177">
-        <v>2174095.69</v>
+        <v>654105.28</v>
       </c>
       <c r="F177">
         <v>0</v>
@@ -5665,7 +5671,7 @@
         <v>237</v>
       </c>
       <c r="H177" s="1">
-        <v>46106</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -5673,22 +5679,22 @@
         <v>46106</v>
       </c>
       <c r="B178">
-        <v>4564</v>
+        <v>4508</v>
       </c>
       <c r="C178" t="s">
         <v>8</v>
       </c>
       <c r="D178" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E178">
-        <v>2366422.64</v>
+        <v>985014.9</v>
       </c>
       <c r="F178">
         <v>0</v>
       </c>
       <c r="G178" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H178" s="1">
         <v>46107</v>
@@ -5699,22 +5705,22 @@
         <v>46106</v>
       </c>
       <c r="B179">
-        <v>4585</v>
+        <v>4526</v>
       </c>
       <c r="C179" t="s">
         <v>8</v>
       </c>
       <c r="D179" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E179">
-        <v>97065.92</v>
+        <v>1676898.11</v>
       </c>
       <c r="F179">
         <v>0</v>
       </c>
       <c r="G179" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H179" s="1">
         <v>46107</v>
@@ -5725,25 +5731,25 @@
         <v>46106</v>
       </c>
       <c r="B180">
-        <v>4599</v>
+        <v>4562</v>
       </c>
       <c r="C180" t="s">
         <v>8</v>
       </c>
       <c r="D180" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E180">
-        <v>2331614.96</v>
+        <v>2174095.69</v>
       </c>
       <c r="F180">
         <v>0</v>
       </c>
       <c r="G180" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H180" s="1">
-        <v>46107</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -5751,22 +5757,22 @@
         <v>46106</v>
       </c>
       <c r="B181">
-        <v>4697</v>
+        <v>4564</v>
       </c>
       <c r="C181" t="s">
         <v>8</v>
       </c>
       <c r="D181" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E181">
-        <v>862670.84</v>
+        <v>2366422.64</v>
       </c>
       <c r="F181">
         <v>0</v>
       </c>
       <c r="G181" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H181" s="1">
         <v>46107</v>
@@ -5774,51 +5780,51 @@
     </row>
     <row r="182" spans="1:8">
       <c r="A182" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B182">
+        <v>4585</v>
+      </c>
+      <c r="C182" t="s">
+        <v>8</v>
+      </c>
+      <c r="D182" t="s">
+        <v>188</v>
+      </c>
+      <c r="E182">
+        <v>97065.92</v>
+      </c>
+      <c r="F182">
+        <v>0</v>
+      </c>
+      <c r="G182" t="s">
+        <v>237</v>
+      </c>
+      <c r="H182" s="1">
         <v>46107</v>
-      </c>
-      <c r="B182">
-        <v>4510</v>
-      </c>
-      <c r="C182" t="s">
-        <v>8</v>
-      </c>
-      <c r="D182" t="s">
-        <v>189</v>
-      </c>
-      <c r="E182">
-        <v>1909696.08</v>
-      </c>
-      <c r="F182">
-        <v>0</v>
-      </c>
-      <c r="G182" t="s">
-        <v>237</v>
-      </c>
-      <c r="H182" s="1">
-        <v>46108</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" s="1">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="B183">
-        <v>4524</v>
+        <v>4599</v>
       </c>
       <c r="C183" t="s">
         <v>8</v>
       </c>
       <c r="D183" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E183">
-        <v>1848570.82</v>
+        <v>2331614.96</v>
       </c>
       <c r="F183">
         <v>0</v>
       </c>
       <c r="G183" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H183" s="1">
         <v>46107</v>
@@ -5826,28 +5832,28 @@
     </row>
     <row r="184" spans="1:8">
       <c r="A184" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B184">
+        <v>4697</v>
+      </c>
+      <c r="C184" t="s">
+        <v>8</v>
+      </c>
+      <c r="D184" t="s">
+        <v>190</v>
+      </c>
+      <c r="E184">
+        <v>862670.84</v>
+      </c>
+      <c r="F184">
+        <v>0</v>
+      </c>
+      <c r="G184" t="s">
+        <v>237</v>
+      </c>
+      <c r="H184" s="1">
         <v>46107</v>
-      </c>
-      <c r="B184">
-        <v>4528</v>
-      </c>
-      <c r="C184" t="s">
-        <v>8</v>
-      </c>
-      <c r="D184" t="s">
-        <v>191</v>
-      </c>
-      <c r="E184">
-        <v>1473563.56</v>
-      </c>
-      <c r="F184">
-        <v>0</v>
-      </c>
-      <c r="G184" t="s">
-        <v>235</v>
-      </c>
-      <c r="H184" s="1">
-        <v>46108</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -5855,25 +5861,25 @@
         <v>46107</v>
       </c>
       <c r="B185">
-        <v>4592</v>
+        <v>4510</v>
       </c>
       <c r="C185" t="s">
         <v>8</v>
       </c>
       <c r="D185" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E185">
-        <v>762809.84</v>
+        <v>1909696.08</v>
       </c>
       <c r="F185">
         <v>0</v>
       </c>
       <c r="G185" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H185" s="1">
-        <v>46107</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -5881,22 +5887,22 @@
         <v>46107</v>
       </c>
       <c r="B186">
-        <v>4612</v>
+        <v>4524</v>
       </c>
       <c r="C186" t="s">
         <v>8</v>
       </c>
       <c r="D186" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E186">
-        <v>255553.1</v>
+        <v>1848570.82</v>
       </c>
       <c r="F186">
         <v>0</v>
       </c>
       <c r="G186" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H186" s="1">
         <v>46107</v>
@@ -5907,16 +5913,16 @@
         <v>46107</v>
       </c>
       <c r="B187">
-        <v>4613</v>
+        <v>4528</v>
       </c>
       <c r="C187" t="s">
         <v>8</v>
       </c>
       <c r="D187" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E187">
-        <v>737829.4</v>
+        <v>1473563.56</v>
       </c>
       <c r="F187">
         <v>0</v>
@@ -5925,7 +5931,7 @@
         <v>237</v>
       </c>
       <c r="H187" s="1">
-        <v>46109</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -5933,22 +5939,22 @@
         <v>46107</v>
       </c>
       <c r="B188">
-        <v>4641</v>
+        <v>4592</v>
       </c>
       <c r="C188" t="s">
         <v>8</v>
       </c>
       <c r="D188" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E188">
-        <v>0</v>
+        <v>762809.84</v>
       </c>
       <c r="F188">
-        <v>1544860.62</v>
+        <v>0</v>
       </c>
       <c r="G188" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H188" s="1">
         <v>46107</v>
@@ -5959,25 +5965,25 @@
         <v>46107</v>
       </c>
       <c r="B189">
-        <v>4676</v>
+        <v>4612</v>
       </c>
       <c r="C189" t="s">
         <v>8</v>
       </c>
       <c r="D189" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E189">
-        <v>0</v>
+        <v>255553.1</v>
       </c>
       <c r="F189">
-        <v>2490017.99</v>
+        <v>0</v>
       </c>
       <c r="G189" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H189" s="1">
-        <v>46108</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -5985,74 +5991,74 @@
         <v>46107</v>
       </c>
       <c r="B190">
-        <v>4698</v>
+        <v>4613</v>
       </c>
       <c r="C190" t="s">
         <v>8</v>
       </c>
       <c r="D190" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E190">
-        <v>395890.79</v>
+        <v>737829.4</v>
       </c>
       <c r="F190">
         <v>0</v>
       </c>
       <c r="G190" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H190" s="1">
-        <v>46107</v>
+        <v>46109</v>
       </c>
     </row>
     <row r="191" spans="1:8">
       <c r="A191" s="1">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="B191">
-        <v>4512</v>
+        <v>4641</v>
       </c>
       <c r="C191" t="s">
         <v>8</v>
       </c>
       <c r="D191" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E191">
-        <v>1134587.49</v>
+        <v>0</v>
       </c>
       <c r="F191">
-        <v>0</v>
+        <v>1544860.62</v>
       </c>
       <c r="G191" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H191" s="1">
-        <v>46110</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="192" spans="1:8">
       <c r="A192" s="1">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="B192">
-        <v>4513</v>
+        <v>4676</v>
       </c>
       <c r="C192" t="s">
         <v>8</v>
       </c>
       <c r="D192" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E192">
-        <v>333923.67</v>
+        <v>0</v>
       </c>
       <c r="F192">
-        <v>0</v>
+        <v>2490017.99</v>
       </c>
       <c r="G192" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H192" s="1">
         <v>46108</v>
@@ -6060,28 +6066,28 @@
     </row>
     <row r="193" spans="1:8">
       <c r="A193" s="1">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="B193">
-        <v>4537</v>
+        <v>4698</v>
       </c>
       <c r="C193" t="s">
         <v>8</v>
       </c>
       <c r="D193" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E193">
-        <v>273636.44</v>
+        <v>395890.79</v>
       </c>
       <c r="F193">
         <v>0</v>
       </c>
       <c r="G193" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H193" s="1">
-        <v>46108</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="194" spans="1:8">
@@ -6089,25 +6095,25 @@
         <v>46108</v>
       </c>
       <c r="B194">
-        <v>4541</v>
+        <v>4512</v>
       </c>
       <c r="C194" t="s">
         <v>8</v>
       </c>
       <c r="D194" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E194">
-        <v>934980.77</v>
+        <v>1134587.49</v>
       </c>
       <c r="F194">
         <v>0</v>
       </c>
       <c r="G194" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H194" s="1">
-        <v>46109</v>
+        <v>46110</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -6115,25 +6121,25 @@
         <v>46108</v>
       </c>
       <c r="B195">
-        <v>4550</v>
+        <v>4513</v>
       </c>
       <c r="C195" t="s">
         <v>8</v>
       </c>
       <c r="D195" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E195">
-        <v>1622908.21</v>
+        <v>333923.67</v>
       </c>
       <c r="F195">
         <v>0</v>
       </c>
       <c r="G195" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H195" s="1">
-        <v>46109</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="196" spans="1:8">
@@ -6141,25 +6147,25 @@
         <v>46108</v>
       </c>
       <c r="B196">
-        <v>4568</v>
+        <v>4537</v>
       </c>
       <c r="C196" t="s">
         <v>8</v>
       </c>
       <c r="D196" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E196">
-        <v>2156854.96</v>
+        <v>273636.44</v>
       </c>
       <c r="F196">
         <v>0</v>
       </c>
       <c r="G196" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H196" s="1">
-        <v>46110</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="197" spans="1:8">
@@ -6167,25 +6173,25 @@
         <v>46108</v>
       </c>
       <c r="B197">
-        <v>4588</v>
+        <v>4541</v>
       </c>
       <c r="C197" t="s">
         <v>8</v>
       </c>
       <c r="D197" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E197">
-        <v>250831.43</v>
+        <v>934980.77</v>
       </c>
       <c r="F197">
         <v>0</v>
       </c>
       <c r="G197" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H197" s="1">
-        <v>46110</v>
+        <v>46109</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -6193,25 +6199,25 @@
         <v>46108</v>
       </c>
       <c r="B198">
-        <v>4603</v>
+        <v>4550</v>
       </c>
       <c r="C198" t="s">
         <v>8</v>
       </c>
       <c r="D198" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E198">
-        <v>1133532.66</v>
+        <v>1622908.21</v>
       </c>
       <c r="F198">
         <v>0</v>
       </c>
       <c r="G198" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="H198" s="1">
-        <v>46110</v>
+        <v>46109</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -6219,25 +6225,25 @@
         <v>46108</v>
       </c>
       <c r="B199">
-        <v>4621</v>
+        <v>4568</v>
       </c>
       <c r="C199" t="s">
         <v>8</v>
       </c>
       <c r="D199" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E199">
-        <v>345451.28</v>
+        <v>2156854.96</v>
       </c>
       <c r="F199">
         <v>0</v>
       </c>
       <c r="G199" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H199" s="1">
-        <v>46109</v>
+        <v>46110</v>
       </c>
     </row>
     <row r="200" spans="1:8">
@@ -6245,25 +6251,25 @@
         <v>46108</v>
       </c>
       <c r="B200">
-        <v>4622</v>
+        <v>4588</v>
       </c>
       <c r="C200" t="s">
         <v>8</v>
       </c>
       <c r="D200" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E200">
-        <v>180786.95</v>
+        <v>250831.43</v>
       </c>
       <c r="F200">
         <v>0</v>
       </c>
       <c r="G200" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H200" s="1">
-        <v>46108</v>
+        <v>46110</v>
       </c>
     </row>
     <row r="201" spans="1:8">
@@ -6271,16 +6277,16 @@
         <v>46108</v>
       </c>
       <c r="B201">
-        <v>4699</v>
+        <v>4603</v>
       </c>
       <c r="C201" t="s">
         <v>8</v>
       </c>
       <c r="D201" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E201">
-        <v>625436.37</v>
+        <v>1133532.66</v>
       </c>
       <c r="F201">
         <v>0</v>
@@ -6289,186 +6295,186 @@
         <v>237</v>
       </c>
       <c r="H201" s="1">
-        <v>46108</v>
+        <v>46110</v>
       </c>
     </row>
     <row r="202" spans="1:8">
       <c r="A202" s="1">
-        <v>46110</v>
+        <v>46108</v>
       </c>
       <c r="B202">
-        <v>4567</v>
+        <v>4621</v>
       </c>
       <c r="C202" t="s">
         <v>8</v>
       </c>
       <c r="D202" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E202">
-        <v>2082418.81</v>
+        <v>345451.28</v>
       </c>
       <c r="F202">
         <v>0</v>
       </c>
       <c r="G202" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H202" s="1">
-        <v>46110</v>
+        <v>46109</v>
       </c>
     </row>
     <row r="203" spans="1:8">
       <c r="A203" s="1">
-        <v>46110</v>
+        <v>46108</v>
       </c>
       <c r="B203">
-        <v>4636</v>
+        <v>4622</v>
       </c>
       <c r="C203" t="s">
         <v>8</v>
       </c>
       <c r="D203" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E203">
-        <v>0</v>
+        <v>180786.95</v>
       </c>
       <c r="F203">
-        <v>2797613.92</v>
+        <v>0</v>
       </c>
       <c r="G203" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H203" s="1">
-        <v>46111</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="204" spans="1:8">
       <c r="A204" s="1">
-        <v>46110</v>
+        <v>46108</v>
       </c>
       <c r="B204">
-        <v>4642</v>
+        <v>4699</v>
       </c>
       <c r="C204" t="s">
         <v>8</v>
       </c>
       <c r="D204" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E204">
-        <v>0</v>
+        <v>625436.37</v>
       </c>
       <c r="F204">
-        <v>2496454.2</v>
+        <v>0</v>
       </c>
       <c r="G204" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="H204" s="1">
-        <v>46110</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="205" spans="1:8">
       <c r="A205" s="1">
-        <v>46111</v>
+        <v>46110</v>
       </c>
       <c r="B205">
-        <v>4700</v>
+        <v>4567</v>
       </c>
       <c r="C205" t="s">
         <v>8</v>
       </c>
       <c r="D205" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E205">
-        <v>201186.6</v>
+        <v>2082418.81</v>
       </c>
       <c r="F205">
         <v>0</v>
       </c>
       <c r="G205" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H205" s="1">
-        <v>46112</v>
+        <v>46110</v>
       </c>
     </row>
     <row r="206" spans="1:8">
       <c r="A206" s="1">
+        <v>46110</v>
+      </c>
+      <c r="B206">
+        <v>4636</v>
+      </c>
+      <c r="C206" t="s">
+        <v>8</v>
+      </c>
+      <c r="D206" t="s">
+        <v>212</v>
+      </c>
+      <c r="E206">
+        <v>0</v>
+      </c>
+      <c r="F206">
+        <v>2797613.92</v>
+      </c>
+      <c r="G206" t="s">
+        <v>238</v>
+      </c>
+      <c r="H206" s="1">
         <v>46111</v>
-      </c>
-      <c r="B206">
-        <v>4723</v>
-      </c>
-      <c r="C206" t="s">
-        <v>8</v>
-      </c>
-      <c r="D206" t="s">
-        <v>213</v>
-      </c>
-      <c r="E206">
-        <v>0</v>
-      </c>
-      <c r="F206">
-        <v>971894.65</v>
-      </c>
-      <c r="G206" t="s">
-        <v>237</v>
-      </c>
-      <c r="H206" s="1">
-        <v>46113</v>
       </c>
     </row>
     <row r="207" spans="1:8">
       <c r="A207" s="1">
-        <v>46112</v>
+        <v>46110</v>
       </c>
       <c r="B207">
-        <v>4674</v>
+        <v>4642</v>
       </c>
       <c r="C207" t="s">
         <v>8</v>
       </c>
       <c r="D207" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E207">
         <v>0</v>
       </c>
       <c r="F207">
-        <v>1758101.64</v>
+        <v>2496454.2</v>
       </c>
       <c r="G207" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H207" s="1">
-        <v>46113</v>
+        <v>46110</v>
       </c>
     </row>
     <row r="208" spans="1:8">
       <c r="A208" s="1">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="B208">
-        <v>4701</v>
+        <v>4700</v>
       </c>
       <c r="C208" t="s">
         <v>8</v>
       </c>
       <c r="D208" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E208">
-        <v>882296.45</v>
+        <v>201186.6</v>
       </c>
       <c r="F208">
         <v>0</v>
       </c>
       <c r="G208" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="H208" s="1">
         <v>46112</v>
@@ -6476,28 +6482,28 @@
     </row>
     <row r="209" spans="1:8">
       <c r="A209" s="1">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="B209">
-        <v>4704</v>
+        <v>4723</v>
       </c>
       <c r="C209" t="s">
         <v>8</v>
       </c>
       <c r="D209" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E209">
         <v>0</v>
       </c>
       <c r="F209">
-        <v>196528.1</v>
+        <v>971894.65</v>
       </c>
       <c r="G209" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="H209" s="1">
-        <v>46115</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -6505,25 +6511,25 @@
         <v>46112</v>
       </c>
       <c r="B210">
-        <v>4705</v>
+        <v>4674</v>
       </c>
       <c r="C210" t="s">
         <v>8</v>
       </c>
       <c r="D210" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E210">
         <v>0</v>
       </c>
       <c r="F210">
-        <v>1271909.61</v>
+        <v>1758101.64</v>
       </c>
       <c r="G210" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H210" s="1">
-        <v>46115</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -6531,440 +6537,518 @@
         <v>46112</v>
       </c>
       <c r="B211">
-        <v>4706</v>
+        <v>4701</v>
       </c>
       <c r="C211" t="s">
         <v>8</v>
       </c>
       <c r="D211" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E211">
-        <v>0</v>
+        <v>882296.45</v>
       </c>
       <c r="F211">
-        <v>184859.53</v>
+        <v>0</v>
       </c>
       <c r="G211" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H211" s="1">
-        <v>46115</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="212" spans="1:8">
       <c r="A212" s="1">
-        <v>46083</v>
+        <v>46112</v>
       </c>
       <c r="B212">
-        <v>4711</v>
+        <v>4704</v>
       </c>
       <c r="C212" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D212" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E212">
         <v>0</v>
       </c>
       <c r="F212">
-        <v>451113.83</v>
+        <v>196528.1</v>
       </c>
       <c r="G212" t="s">
         <v>237</v>
       </c>
       <c r="H212" s="1">
-        <v>46083</v>
+        <v>46115</v>
       </c>
     </row>
     <row r="213" spans="1:8">
       <c r="A213" s="1">
-        <v>46087</v>
+        <v>46112</v>
       </c>
       <c r="B213">
-        <v>4712</v>
+        <v>4705</v>
       </c>
       <c r="C213" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D213" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E213">
         <v>0</v>
       </c>
       <c r="F213">
-        <v>252483.44</v>
+        <v>1271909.61</v>
       </c>
       <c r="G213" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H213" s="1">
-        <v>46088</v>
+        <v>46115</v>
       </c>
     </row>
     <row r="214" spans="1:8">
       <c r="A214" s="1">
-        <v>46087</v>
+        <v>46112</v>
       </c>
       <c r="B214">
-        <v>4718</v>
+        <v>4706</v>
       </c>
       <c r="C214" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D214" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E214">
         <v>0</v>
       </c>
       <c r="F214">
-        <v>219847.69</v>
+        <v>184859.53</v>
       </c>
       <c r="G214" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H214" s="1">
-        <v>46087</v>
+        <v>46115</v>
       </c>
     </row>
     <row r="215" spans="1:8">
       <c r="A215" s="1">
-        <v>46091</v>
+        <v>46083</v>
       </c>
       <c r="B215">
-        <v>4710</v>
+        <v>4711</v>
       </c>
       <c r="C215" t="s">
         <v>9</v>
       </c>
       <c r="D215" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E215">
         <v>0</v>
       </c>
       <c r="F215">
-        <v>592690.84</v>
+        <v>451113.83</v>
       </c>
       <c r="G215" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H215" s="1">
-        <v>46093</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="216" spans="1:8">
       <c r="A216" s="1">
-        <v>46091</v>
+        <v>46087</v>
       </c>
       <c r="B216">
-        <v>4715</v>
+        <v>4712</v>
       </c>
       <c r="C216" t="s">
         <v>9</v>
       </c>
       <c r="D216" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E216">
         <v>0</v>
       </c>
       <c r="F216">
-        <v>378143.19</v>
+        <v>252483.44</v>
       </c>
       <c r="G216" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H216" s="1">
-        <v>46091</v>
+        <v>46088</v>
       </c>
     </row>
     <row r="217" spans="1:8">
       <c r="A217" s="1">
-        <v>46094</v>
+        <v>46087</v>
       </c>
       <c r="B217">
-        <v>4709</v>
+        <v>4718</v>
       </c>
       <c r="C217" t="s">
         <v>9</v>
       </c>
       <c r="D217" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E217">
         <v>0</v>
       </c>
       <c r="F217">
-        <v>451920.16</v>
+        <v>219847.69</v>
       </c>
       <c r="G217" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H217" s="1">
-        <v>46095</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="218" spans="1:8">
       <c r="A218" s="1">
-        <v>46098</v>
+        <v>46091</v>
       </c>
       <c r="B218">
-        <v>4722</v>
+        <v>4710</v>
       </c>
       <c r="C218" t="s">
         <v>9</v>
       </c>
       <c r="D218" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E218">
         <v>0</v>
       </c>
       <c r="F218">
-        <v>637092.53</v>
+        <v>592690.84</v>
       </c>
       <c r="G218" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H218" s="1">
-        <v>46099</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="219" spans="1:8">
       <c r="A219" s="1">
-        <v>46099</v>
+        <v>46091</v>
       </c>
       <c r="B219">
-        <v>4721</v>
+        <v>4715</v>
       </c>
       <c r="C219" t="s">
         <v>9</v>
       </c>
       <c r="D219" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E219">
         <v>0</v>
       </c>
       <c r="F219">
-        <v>536057.91</v>
+        <v>378143.19</v>
       </c>
       <c r="G219" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H219" s="1">
-        <v>46099</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="220" spans="1:8">
       <c r="A220" s="1">
-        <v>46104</v>
+        <v>46094</v>
       </c>
       <c r="B220">
-        <v>4714</v>
+        <v>4709</v>
       </c>
       <c r="C220" t="s">
         <v>9</v>
       </c>
       <c r="D220" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E220">
         <v>0</v>
       </c>
       <c r="F220">
-        <v>219189.04</v>
+        <v>451920.16</v>
       </c>
       <c r="G220" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="H220" s="1">
-        <v>46106</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="221" spans="1:8">
       <c r="A221" s="1">
-        <v>46104</v>
+        <v>46098</v>
       </c>
       <c r="B221">
-        <v>4717</v>
+        <v>4722</v>
       </c>
       <c r="C221" t="s">
         <v>9</v>
       </c>
       <c r="D221" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E221">
         <v>0</v>
       </c>
       <c r="F221">
-        <v>67893.96000000001</v>
+        <v>637092.53</v>
       </c>
       <c r="G221" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H221" s="1">
-        <v>46104</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="222" spans="1:8">
       <c r="A222" s="1">
-        <v>46105</v>
+        <v>46099</v>
       </c>
       <c r="B222">
-        <v>4716</v>
+        <v>4721</v>
       </c>
       <c r="C222" t="s">
         <v>9</v>
       </c>
       <c r="D222" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E222">
         <v>0</v>
       </c>
       <c r="F222">
-        <v>515904.01</v>
+        <v>536057.91</v>
       </c>
       <c r="G222" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H222" s="1">
-        <v>46105</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="223" spans="1:8">
       <c r="A223" s="1">
-        <v>46106</v>
+        <v>46104</v>
       </c>
       <c r="B223">
-        <v>4713</v>
+        <v>4714</v>
       </c>
       <c r="C223" t="s">
         <v>9</v>
       </c>
       <c r="D223" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E223">
         <v>0</v>
       </c>
       <c r="F223">
-        <v>297129.05</v>
+        <v>219189.04</v>
       </c>
       <c r="G223" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H223" s="1">
-        <v>46108</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="224" spans="1:8">
       <c r="A224" s="1">
-        <v>46106</v>
+        <v>46104</v>
       </c>
       <c r="B224">
-        <v>4720</v>
+        <v>4717</v>
       </c>
       <c r="C224" t="s">
         <v>9</v>
       </c>
       <c r="D224" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E224">
         <v>0</v>
       </c>
       <c r="F224">
-        <v>458053.77</v>
+        <v>67893.96000000001</v>
       </c>
       <c r="G224" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H224" s="1">
-        <v>46108</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="225" spans="1:8">
       <c r="A225" s="1">
-        <v>46108</v>
+        <v>46105</v>
       </c>
       <c r="B225">
-        <v>4719</v>
+        <v>4716</v>
       </c>
       <c r="C225" t="s">
         <v>9</v>
       </c>
       <c r="D225" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E225">
         <v>0</v>
       </c>
       <c r="F225">
-        <v>276603.37</v>
+        <v>515904.01</v>
       </c>
       <c r="G225" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H225" s="1">
-        <v>46108</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="226" spans="1:8">
       <c r="A226" s="1">
-        <v>46112</v>
+        <v>46106</v>
       </c>
       <c r="B226">
-        <v>4707</v>
+        <v>4713</v>
       </c>
       <c r="C226" t="s">
         <v>9</v>
       </c>
       <c r="D226" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E226">
-        <v>5773361.05</v>
+        <v>0</v>
       </c>
       <c r="F226">
-        <v>0</v>
+        <v>297129.05</v>
       </c>
       <c r="G226" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H226" s="1">
-        <v>46114</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="227" spans="1:8">
       <c r="A227" s="1">
-        <v>46112</v>
+        <v>46106</v>
       </c>
       <c r="B227">
-        <v>4708</v>
+        <v>4720</v>
       </c>
       <c r="C227" t="s">
         <v>9</v>
       </c>
       <c r="D227" t="s">
+        <v>233</v>
+      </c>
+      <c r="E227">
+        <v>0</v>
+      </c>
+      <c r="F227">
+        <v>458053.77</v>
+      </c>
+      <c r="G227" t="s">
+        <v>237</v>
+      </c>
+      <c r="H227" s="1">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8">
+      <c r="A228" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B228">
+        <v>4719</v>
+      </c>
+      <c r="C228" t="s">
+        <v>9</v>
+      </c>
+      <c r="D228" t="s">
         <v>234</v>
       </c>
-      <c r="E227">
-        <v>0</v>
-      </c>
-      <c r="F227">
+      <c r="E228">
+        <v>0</v>
+      </c>
+      <c r="F228">
+        <v>276603.37</v>
+      </c>
+      <c r="G228" t="s">
+        <v>238</v>
+      </c>
+      <c r="H228" s="1">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8">
+      <c r="A229" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B229">
+        <v>4707</v>
+      </c>
+      <c r="C229" t="s">
+        <v>9</v>
+      </c>
+      <c r="D229" t="s">
+        <v>235</v>
+      </c>
+      <c r="E229">
+        <v>5773361.05</v>
+      </c>
+      <c r="F229">
+        <v>0</v>
+      </c>
+      <c r="G229" t="s">
+        <v>239</v>
+      </c>
+      <c r="H229" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8">
+      <c r="A230" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B230">
+        <v>4708</v>
+      </c>
+      <c r="C230" t="s">
+        <v>9</v>
+      </c>
+      <c r="D230" t="s">
+        <v>236</v>
+      </c>
+      <c r="E230">
+        <v>0</v>
+      </c>
+      <c r="F230">
         <v>30393.47</v>
       </c>
-      <c r="G227" t="s">
-        <v>235</v>
-      </c>
-      <c r="H227" s="1">
+      <c r="G230" t="s">
+        <v>237</v>
+      </c>
+      <c r="H230" s="1">
         <v>46114</v>
       </c>
     </row>
